--- a/KiCad /BOM xsl/bomn.xlsx
+++ b/KiCad /BOM xsl/bomn.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Soletop\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0EE87C0-86FB-4958-A97F-A6324A632576}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB3ACDE2-3752-43A2-8DE6-6CCAD0D0DA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16810" yWindow="4380" windowWidth="21690" windowHeight="14330" xr2:uid="{4B84FC1E-AEA6-428E-A39B-C2CBD48CACA0}"/>
+    <workbookView xWindow="-430" yWindow="5400" windowWidth="18000" windowHeight="14330" xr2:uid="{4B84FC1E-AEA6-428E-A39B-C2CBD48CACA0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="119">
   <si>
     <t>C1</t>
   </si>
@@ -447,6 +447,142 @@
       </rPr>
       <t>Ω</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C22936</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1779</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C45783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C167925</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C7420328</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C5438410</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C2297</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C177241</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C725790</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C116741</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C206167</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C3749797</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C84256</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C20615782</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C20615806</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C4211</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C25804</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C23140</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C22976</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C23137</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C22961</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C22935</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C23162</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C21190</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C23186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C25803</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C17928</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C13585</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1710</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C14663</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C377773</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1588</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C15849</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C440198</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -500,12 +636,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -874,6 +1013,9 @@
       <c r="C2" t="s">
         <v>36</v>
       </c>
+      <c r="D2" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
@@ -885,6 +1027,9 @@
       <c r="C3" t="s">
         <v>37</v>
       </c>
+      <c r="D3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -896,6 +1041,9 @@
       <c r="C4" t="s">
         <v>36</v>
       </c>
+      <c r="D4" t="s">
+        <v>87</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
@@ -907,6 +1055,9 @@
       <c r="C5" t="s">
         <v>38</v>
       </c>
+      <c r="D5" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -916,7 +1067,10 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="D6" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
@@ -929,6 +1083,9 @@
       <c r="C7" t="s">
         <v>38</v>
       </c>
+      <c r="D7" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -940,6 +1097,9 @@
       <c r="C8" t="s">
         <v>39</v>
       </c>
+      <c r="D8" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
@@ -951,6 +1111,9 @@
       <c r="C9" t="s">
         <v>36</v>
       </c>
+      <c r="D9" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -962,6 +1125,9 @@
       <c r="C10" t="s">
         <v>38</v>
       </c>
+      <c r="D10" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
@@ -973,6 +1139,9 @@
       <c r="C11" t="s">
         <v>36</v>
       </c>
+      <c r="D11" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
@@ -984,6 +1153,9 @@
       <c r="C12" t="s">
         <v>40</v>
       </c>
+      <c r="D12" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
@@ -995,6 +1167,9 @@
       <c r="C13" t="s">
         <v>40</v>
       </c>
+      <c r="D13" t="s">
+        <v>91</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
@@ -1006,6 +1181,9 @@
       <c r="C14" t="s">
         <v>41</v>
       </c>
+      <c r="D14" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
@@ -1017,6 +1195,9 @@
       <c r="C15" t="s">
         <v>42</v>
       </c>
+      <c r="D15" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
@@ -1028,8 +1209,11 @@
       <c r="C16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D16" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>66</v>
       </c>
@@ -1039,8 +1223,11 @@
       <c r="C17" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D17" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>67</v>
       </c>
@@ -1050,8 +1237,11 @@
       <c r="C18" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>68</v>
       </c>
@@ -1061,8 +1251,11 @@
       <c r="C19" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D19" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>72</v>
       </c>
@@ -1072,8 +1265,11 @@
       <c r="C20" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D20" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>73</v>
       </c>
@@ -1083,8 +1279,11 @@
       <c r="C21" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D21" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>74</v>
       </c>
@@ -1094,8 +1293,11 @@
       <c r="C22" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D22" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>75</v>
       </c>
@@ -1105,8 +1307,11 @@
       <c r="C23" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D23" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>77</v>
       </c>
@@ -1116,8 +1321,11 @@
       <c r="C24" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D24" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>78</v>
       </c>
@@ -1127,8 +1335,11 @@
       <c r="C25" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>79</v>
       </c>
@@ -1138,8 +1349,11 @@
       <c r="C26" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D26" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A27" t="s">
         <v>80</v>
       </c>
@@ -1149,8 +1363,11 @@
       <c r="C27" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A28" t="s">
         <v>81</v>
       </c>
@@ -1160,8 +1377,11 @@
       <c r="C28" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A29" t="s">
         <v>82</v>
       </c>
@@ -1171,8 +1391,11 @@
       <c r="C29" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A30" t="s">
         <v>83</v>
       </c>
@@ -1182,8 +1405,11 @@
       <c r="C30" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A31" t="s">
         <v>84</v>
       </c>
@@ -1193,8 +1419,11 @@
       <c r="C31" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D31" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A32" t="s">
         <v>81</v>
       </c>
@@ -1204,8 +1433,11 @@
       <c r="C32" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D32" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
         <v>69</v>
       </c>
@@ -1215,8 +1447,11 @@
       <c r="C33" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D33" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
         <v>70</v>
       </c>
@@ -1226,8 +1461,11 @@
       <c r="C34" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="D34" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
         <v>71</v>
       </c>
@@ -1236,6 +1474,9 @@
       </c>
       <c r="C35" t="s">
         <v>51</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>95</v>
       </c>
     </row>
   </sheetData>
